--- a/output/sliding_window_results_window_8.xlsx
+++ b/output/sliding_window_results_window_8.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C2" t="n">
-        <v>30.21698459963282</v>
+        <v>48.45784981290348</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.063015400367181</v>
+        <v>4.757849812903473</v>
       </c>
       <c r="E2" t="n">
-        <v>4.256032542152161</v>
+        <v>22.63713484214561</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C3" t="n">
-        <v>32.108692325862</v>
+        <v>53.05045428692944</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.9913076741379996</v>
+        <v>4.950454286929435</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9826909048048904</v>
+        <v>24.50699764697803</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>33.65796870577914</v>
+        <v>58.51178909674051</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.7420312942208582</v>
+        <v>5.511789096740507</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5506104416030819</v>
+        <v>30.37981904694754</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C5" t="n">
-        <v>35.11317575329436</v>
+        <v>65.01843109193067</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.18682424670564</v>
+        <v>8.918431091930664</v>
       </c>
       <c r="E5" t="n">
-        <v>1.408551792568411</v>
+        <v>79.53841314151558</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>35.87530513452462</v>
+        <v>65.67661021180356</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.624694865475377</v>
+        <v>5.676610211803563</v>
       </c>
       <c r="E6" t="n">
-        <v>6.889023136852805</v>
+        <v>32.2239034967525</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C7" t="n">
-        <v>37.91809027305864</v>
+        <v>71.31807751652799</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.181909726941363</v>
+        <v>7.418077516527994</v>
       </c>
       <c r="E7" t="n">
-        <v>4.760730056521334</v>
+        <v>55.02787404121813</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>39.87421433690742</v>
+        <v>77.17472748595284</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.625785663092579</v>
+        <v>6.574727485952849</v>
       </c>
       <c r="E8" t="n">
-        <v>2.643179022317376</v>
+        <v>43.22704151454387</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>43.27877681779365</v>
+        <v>89.592039561118</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4212231822063544</v>
+        <v>8.692039561117994</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1774289692280476</v>
+        <v>75.55155173204029</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>44.10126348395841</v>
+        <v>97.49285066818518</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.998736516041596</v>
+        <v>8.39285066818519</v>
       </c>
       <c r="E10" t="n">
-        <v>15.98989372472448</v>
+        <v>70.43994233845659</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C11" t="n">
-        <v>48.37329724963767</v>
+        <v>87.42489798226428</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.626702750362327</v>
+        <v>-7.575102017735716</v>
       </c>
       <c r="E11" t="n">
-        <v>21.40637834021032</v>
+        <v>57.38217057910372</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C12" t="n">
-        <v>53.80945865463663</v>
+        <v>99.79260534793188</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.290541345363373</v>
+        <v>0.9926053479318853</v>
       </c>
       <c r="E12" t="n">
-        <v>5.246579654819049</v>
+        <v>0.985265376742979</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C13" t="n">
-        <v>57.09558385315501</v>
+        <v>104.8265782253334</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.904416146844994</v>
+        <v>1.526578225333409</v>
       </c>
       <c r="E13" t="n">
-        <v>8.435633154053923</v>
+        <v>2.330441078062102</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C14" t="n">
-        <v>60.50754956179455</v>
+        <v>113.78701151388</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.392450438205444</v>
+        <v>6.787011513880046</v>
       </c>
       <c r="E14" t="n">
-        <v>11.50871997568031</v>
+        <v>46.06352528954031</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C15" t="n">
-        <v>67.9801765663948</v>
+        <v>119.9442879472199</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.619823433605191</v>
+        <v>11.24428794721995</v>
       </c>
       <c r="E15" t="n">
-        <v>6.863474823266893</v>
+        <v>126.4340114399957</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C16" t="n">
-        <v>74.97173907017054</v>
+        <v>121.682088701004</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.928260929829463</v>
+        <v>8.982088701003988</v>
       </c>
       <c r="E16" t="n">
-        <v>35.14427765214249</v>
+        <v>80.67791743270351</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C17" t="n">
-        <v>84.24019503193861</v>
+        <v>128.1343145966937</v>
       </c>
       <c r="D17" t="n">
-        <v>-4.859804968061383</v>
+        <v>10.93431459669368</v>
       </c>
       <c r="E17" t="n">
-        <v>23.6177043275941</v>
+        <v>119.5592356994685</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C18" t="n">
-        <v>90.03226015634286</v>
+        <v>130.9251371538142</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.967739843657142</v>
+        <v>7.825137153814183</v>
       </c>
       <c r="E18" t="n">
-        <v>24.67843915425869</v>
+        <v>61.23277147600312</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C19" t="n">
-        <v>94.74254297765029</v>
+        <v>130.6511841770522</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.057457022349709</v>
+        <v>1.75118417705221</v>
       </c>
       <c r="E19" t="n">
-        <v>16.46295748821497</v>
+        <v>3.066646021958025</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>103.3</v>
+        <v>135.1</v>
       </c>
       <c r="C20" t="n">
-        <v>99.58319902918669</v>
+        <v>144.6949793368536</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.71680097081331</v>
+        <v>9.59497933685364</v>
       </c>
       <c r="E20" t="n">
-        <v>13.81460945663876</v>
+        <v>92.06362847464833</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>107</v>
+        <v>139.4</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0945350431046</v>
+        <v>152.5215133342373</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.905464956895429</v>
+        <v>13.12151333423728</v>
       </c>
       <c r="E21" t="n">
-        <v>34.87451635711993</v>
+        <v>172.1741121805667</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-61.10499137517671</v>
+        <v>126.0774280483762</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>239.711430974772</v>
+        <v>1195.502402849391</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>11.9855715487386</v>
+        <v>59.77512014246956</v>
       </c>
     </row>
   </sheetData>
